--- a/tests/traces/h100/Qwen_Qwen1.5-0.5B-Chat__1016005_perf_report.xlsx
+++ b/tests/traces/h100/Qwen_Qwen1.5-0.5B-Chat__1016005_perf_report.xlsx
@@ -14,8 +14,8 @@
     <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="SDPA_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="UnaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="BinaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Reduce_fwd" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="kernel_summary" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="short_kernel_histogram" sheetId="12" state="visible" r:id="rId12"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(743.3270000000001), 'mean_duration_us': np.float64(15.169938775510206), 'median_duration_us': np.float64(15.072), 'std_dev_duration_us': np.float64(0.46419596531071383), 'min_duration_us': np.float64(14.176), 'max_duration_us': np.float64(16.449)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt;)', 'stream': 7, 'gpu_op_uid': 11987, 'count': 49, 'total_duration_us': np.float64(743.3270000000001), 'mean_duration_us': np.float64(15.169938775510206), 'median_duration_us': np.float64(15.072), 'std_dev_duration_us': np.float64(0.46419596531071383), 'min_duration_us': np.float64(14.176), 'max_duration_us': np.float64(16.449)}]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(39.75), 'mean_duration_us': np.float64(0.828125), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.07937112851450877), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.057)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(4015.5009999999997), 'mean_duration_us': np.float64(83.65627083333332), 'median_duration_us': np.float64(83.679), 'std_dev_duration_us': np.float64(1.1791844593401435), 'min_duration_us': np.float64(81.472), 'max_duration_us': np.float64(86.016)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 12177, 'count': 48, 'total_duration_us': np.float64(39.75), 'mean_duration_us': np.float64(0.828125), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.07937112851450877), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.057)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 12187, 'count': 48, 'total_duration_us': np.float64(4015.5009999999997), 'mean_duration_us': np.float64(83.65627083333332), 'median_duration_us': np.float64(83.679), 'std_dev_duration_us': np.float64(1.1791844593401435), 'min_duration_us': np.float64(81.472), 'max_duration_us': np.float64(86.016)}]</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, true, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(2722.705), 'mean_duration_us': np.float64(113.44604166666666), 'median_duration_us': np.float64(113.775), 'std_dev_duration_us': np.float64(2.127694555913488), 'min_duration_us': np.float64(109.28), 'max_duration_us': np.float64(119.647)}]</t>
+          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, true, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'gpu_op_uid': 12115, 'count': 24, 'total_duration_us': np.float64(2722.705), 'mean_duration_us': np.float64(113.44604166666666), 'median_duration_us': np.float64(113.775), 'std_dev_duration_us': np.float64(2.127694555913488), 'min_duration_us': np.float64(109.28), 'max_duration_us': np.float64(119.647)}]</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(62.783), 'mean_duration_us': np.float64(0.8719861111111111), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.11567921318307071), 'min_duration_us': np.float64(0.767), 'max_duration_us': np.float64(1.216)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(2266.292), 'mean_duration_us': np.float64(31.476277777777778), 'median_duration_us': np.float64(31.456), 'std_dev_duration_us': np.float64(0.31881400107892144), 'min_duration_us': np.float64(30.912), 'max_duration_us': np.float64(32.256)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 12013, 'count': 72, 'total_duration_us': np.float64(62.783), 'mean_duration_us': np.float64(0.8719861111111111), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.11567921318307071), 'min_duration_us': np.float64(0.767), 'max_duration_us': np.float64(1.216)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 12023, 'count': 72, 'total_duration_us': np.float64(2266.292), 'mean_duration_us': np.float64(31.476277777777778), 'median_duration_us': np.float64(31.456), 'std_dev_duration_us': np.float64(0.31881400107892144), 'min_duration_us': np.float64(30.912), 'max_duration_us': np.float64(32.256)}]</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(2108.187), 'mean_duration_us': np.float64(29.280375), 'median_duration_us': np.float64(29.312), 'std_dev_duration_us': np.float64(0.3210814381594732), 'min_duration_us': np.float64(28.672), 'max_duration_us': np.float64(30.048)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 12099, 'count': 72, 'total_duration_us': np.float64(2108.187), 'mean_duration_us': np.float64(29.280375), 'median_duration_us': np.float64(29.312), 'std_dev_duration_us': np.float64(0.3210814381594732), 'min_duration_us': np.float64(28.672), 'max_duration_us': np.float64(30.048)}]</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 4, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(2014.326), 'mean_duration_us': np.float64(41.965125), 'median_duration_us': np.float64(41.968), 'std_dev_duration_us': np.float64(0.290296301575362), 'min_duration_us': np.float64(41.376), 'max_duration_us': np.float64(42.464)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 4, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'gpu_op_uid': 12067, 'count': 48, 'total_duration_us': np.float64(2014.326), 'mean_duration_us': np.float64(41.965125), 'median_duration_us': np.float64(41.968), 'std_dev_duration_us': np.float64(0.290296301575362), 'min_duration_us': np.float64(41.376), 'max_duration_us': np.float64(42.464)}]</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.512999999999998), 'mean_duration_us': np.float64(0.8547083333333333), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.10426427926454754), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.088)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1814.774), 'mean_duration_us': np.float64(75.61558333333333), 'median_duration_us': np.float64(75.6315), 'std_dev_duration_us': np.float64(0.4239531142184896), 'min_duration_us': np.float64(74.752), 'max_duration_us': np.float64(76.384)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 12217, 'count': 24, 'total_duration_us': np.float64(20.512999999999998), 'mean_duration_us': np.float64(0.8547083333333333), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.10426427926454754), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.088)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 12227, 'count': 24, 'total_duration_us': np.float64(1814.774), 'mean_duration_us': np.float64(75.61558333333333), 'median_duration_us': np.float64(75.6315), 'std_dev_duration_us': np.float64(0.4239531142184896), 'min_duration_us': np.float64(74.752), 'max_duration_us': np.float64(76.384)}]</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(1671.096), 'mean_duration_us': np.float64(34.8145), 'median_duration_us': np.float64(34.784), 'std_dev_duration_us': np.float64(0.3216488121124247), 'min_duration_us': np.float64(34.271), 'max_duration_us': np.float64(35.615)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 12075, 'count': 48, 'total_duration_us': np.float64(1671.096), 'mean_duration_us': np.float64(34.8145), 'median_duration_us': np.float64(34.784), 'std_dev_duration_us': np.float64(0.3216488121124247), 'min_duration_us': np.float64(34.271), 'max_duration_us': np.float64(35.615)}]</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 2, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1608.9229999999998), 'mean_duration_us': np.float64(32.835163265306115), 'median_duration_us': np.float64(32.64), 'std_dev_duration_us': np.float64(0.42625121207266925), 'min_duration_us': np.float64(32.256), 'max_duration_us': np.float64(33.887)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 2, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 11999, 'count': 49, 'total_duration_us': np.float64(1608.9229999999998), 'mean_duration_us': np.float64(32.835163265306115), 'median_duration_us': np.float64(32.64), 'std_dev_duration_us': np.float64(0.42625121207266925), 'min_duration_us': np.float64(32.256), 'max_duration_us': np.float64(33.887)}]</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(1537.849), 'mean_duration_us': np.float64(32.03852083333333), 'median_duration_us': np.float64(32.0), 'std_dev_duration_us': np.float64(0.31526120054007917), 'min_duration_us': np.float64(31.552), 'max_duration_us': np.float64(32.672)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 12059, 'count': 48, 'total_duration_us': np.float64(1537.849), 'mean_duration_us': np.float64(32.03852083333333), 'median_duration_us': np.float64(32.0), 'std_dev_duration_us': np.float64(0.31526120054007917), 'min_duration_us': np.float64(31.552), 'max_duration_us': np.float64(32.672)}]</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1431.6720000000003), 'mean_duration_us': np.float64(29.21779591836735), 'median_duration_us': np.float64(29.216), 'std_dev_duration_us': np.float64(0.6654753090251477), 'min_duration_us': np.float64(25.247), 'max_duration_us': np.float64(30.049)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'gpu_op_uid': 11979, 'count': 49, 'total_duration_us': np.float64(1431.6720000000003), 'mean_duration_us': np.float64(29.21779591836735), 'median_duration_us': np.float64(29.216), 'std_dev_duration_us': np.float64(0.6654753090251477), 'min_duration_us': np.float64(25.247), 'max_duration_us': np.float64(30.049)}]</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1300.7949999999998), 'mean_duration_us': np.float64(26.546836734693873), 'median_duration_us': np.float64(26.4), 'std_dev_duration_us': np.float64(0.41517418753759416), 'min_duration_us': np.float64(26.048), 'max_duration_us': np.float64(27.552)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 11983, 'count': 49, 'total_duration_us': np.float64(1300.7949999999998), 'mean_duration_us': np.float64(26.546836734693873), 'median_duration_us': np.float64(26.4), 'std_dev_duration_us': np.float64(0.41517418753759416), 'min_duration_us': np.float64(26.048), 'max_duration_us': np.float64(27.552)}]</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1233.979), 'mean_duration_us': np.float64(25.183244897959185), 'median_duration_us': np.float64(25.088), 'std_dev_duration_us': np.float64(0.3931505673357448), 'min_duration_us': np.float64(24.576), 'max_duration_us': np.float64(26.144)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 12007, 'count': 49, 'total_duration_us': np.float64(1233.979), 'mean_duration_us': np.float64(25.183244897959185), 'median_duration_us': np.float64(25.088), 'std_dev_duration_us': np.float64(0.3931505673357448), 'min_duration_us': np.float64(24.576), 'max_duration_us': np.float64(26.144)}]</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1227.131), 'mean_duration_us': np.float64(51.13045833333334), 'median_duration_us': np.float64(51.072), 'std_dev_duration_us': np.float64(0.617469161117019), 'min_duration_us': np.float64(50.176), 'max_duration_us': np.float64(52.095)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'gpu_op_uid': 12211, 'count': 24, 'total_duration_us': np.float64(1227.131), 'mean_duration_us': np.float64(51.13045833333334), 'median_duration_us': np.float64(51.072), 'std_dev_duration_us': np.float64(0.617469161117019), 'min_duration_us': np.float64(50.176), 'max_duration_us': np.float64(52.095)}]</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(1141.883), 'mean_duration_us': np.float64(23.78922916666667), 'median_duration_us': np.float64(23.776), 'std_dev_duration_us': np.float64(0.18074236263063953), 'min_duration_us': np.float64(23.392), 'max_duration_us': np.float64(24.352)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 12071, 'count': 48, 'total_duration_us': np.float64(1141.883), 'mean_duration_us': np.float64(23.78922916666667), 'median_duration_us': np.float64(23.776), 'std_dev_duration_us': np.float64(0.18074236263063953), 'min_duration_us': np.float64(23.392), 'max_duration_us': np.float64(24.352)}]</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(925.115), 'mean_duration_us': np.float64(38.546458333333334), 'median_duration_us': np.float64(38.416), 'std_dev_duration_us': np.float64(0.35488331171042203), 'min_duration_us': np.float64(38.144), 'max_duration_us': np.float64(39.264)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 12191, 'count': 24, 'total_duration_us': np.float64(925.115), 'mean_duration_us': np.float64(38.546458333333334), 'median_duration_us': np.float64(38.416), 'std_dev_duration_us': np.float64(0.35488331171042203), 'min_duration_us': np.float64(38.144), 'max_duration_us': np.float64(39.264)}]</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(898.427), 'mean_duration_us': np.float64(18.335244897959186), 'median_duration_us': np.float64(18.24), 'std_dev_duration_us': np.float64(0.36088720215331926), 'min_duration_us': np.float64(17.855), 'max_duration_us': np.float64(19.52)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 12003, 'count': 49, 'total_duration_us': np.float64(898.427), 'mean_duration_us': np.float64(18.335244897959186), 'median_duration_us': np.float64(18.24), 'std_dev_duration_us': np.float64(0.36088720215331926), 'min_duration_us': np.float64(17.855), 'max_duration_us': np.float64(19.52)}]</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(854.619), 'mean_duration_us': np.float64(17.8045625), 'median_duration_us': np.float64(17.856), 'std_dev_duration_us': np.float64(0.5150970744371872), 'min_duration_us': np.float64(17.056), 'max_duration_us': np.float64(19.008)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'gpu_op_uid': 12139, 'count': 48, 'total_duration_us': np.float64(854.619), 'mean_duration_us': np.float64(17.8045625), 'median_duration_us': np.float64(17.856), 'std_dev_duration_us': np.float64(0.5150970744371872), 'min_duration_us': np.float64(17.056), 'max_duration_us': np.float64(19.008)}]</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.001000000000005), 'mean_duration_us': np.float64(0.8333750000000002), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.08185037797713582), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.056)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(758.1399999999999), 'mean_duration_us': np.float64(31.58916666666666), 'median_duration_us': np.float64(31.552), 'std_dev_duration_us': np.float64(0.15096182372448408), 'min_duration_us': np.float64(31.392), 'max_duration_us': np.float64(31.936)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 12125, 'count': 24, 'total_duration_us': np.float64(20.001000000000005), 'mean_duration_us': np.float64(0.8333750000000002), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.08185037797713582), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.056)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 12135, 'count': 24, 'total_duration_us': np.float64(758.1399999999999), 'mean_duration_us': np.float64(31.58916666666666), 'median_duration_us': np.float64(31.552), 'std_dev_duration_us': np.float64(0.15096182372448408), 'min_duration_us': np.float64(31.392), 'max_duration_us': np.float64(31.936)}]</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(743.3270000000001), 'mean_duration_us': np.float64(15.169938775510206), 'median_duration_us': np.float64(15.072), 'std_dev_duration_us': np.float64(0.46419596531071383), 'min_duration_us': np.float64(14.176), 'max_duration_us': np.float64(16.449)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt;)', 'stream': 7, 'gpu_op_uid': 11987, 'count': 49, 'total_duration_us': np.float64(743.3270000000001), 'mean_duration_us': np.float64(15.169938775510206), 'median_duration_us': np.float64(15.072), 'std_dev_duration_us': np.float64(0.46419596531071383), 'min_duration_us': np.float64(14.176), 'max_duration_us': np.float64(16.449)}]</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(658.0799999999999), 'mean_duration_us': np.float64(27.419999999999998), 'median_duration_us': np.float64(27.456), 'std_dev_duration_us': np.float64(0.2218289506203673), 'min_duration_us': np.float64(26.913), 'max_duration_us': np.float64(27.872)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 12119, 'count': 24, 'total_duration_us': np.float64(658.0799999999999), 'mean_duration_us': np.float64(27.419999999999998), 'median_duration_us': np.float64(27.456), 'std_dev_duration_us': np.float64(0.2218289506203673), 'min_duration_us': np.float64(26.913), 'max_duration_us': np.float64(27.872)}]</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(587.328), 'mean_duration_us': np.float64(12.235999999999999), 'median_duration_us': np.float64(12.192), 'std_dev_duration_us': np.float64(0.3355813363900522), 'min_duration_us': np.float64(11.616), 'max_duration_us': np.float64(13.28)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 12063, 'count': 48, 'total_duration_us': np.float64(587.328), 'mean_duration_us': np.float64(12.235999999999999), 'median_duration_us': np.float64(12.192), 'std_dev_duration_us': np.float64(0.3355813363900522), 'min_duration_us': np.float64(11.616), 'max_duration_us': np.float64(13.28)}]</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(81.797), 'mean_duration_us': np.float64(1.669326530612245), 'median_duration_us': np.float64(1.632), 'std_dev_duration_us': np.float64(0.08264514449362109), 'min_duration_us': np.float64(1.568), 'max_duration_us': np.float64(1.952)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 11991, 'count': 49, 'total_duration_us': np.float64(81.797), 'mean_duration_us': np.float64(1.669326530612245), 'median_duration_us': np.float64(1.632), 'std_dev_duration_us': np.float64(0.08264514449362109), 'min_duration_us': np.float64(1.568), 'max_duration_us': np.float64(1.952)}]</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(79.073), 'mean_duration_us': np.float64(1.613734693877551), 'median_duration_us': np.float64(1.6), 'std_dev_duration_us': np.float64(0.10155782016738636), 'min_duration_us': np.float64(1.536), 'max_duration_us': np.float64(2.176)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 11995, 'count': 49, 'total_duration_us': np.float64(79.073), 'mean_duration_us': np.float64(1.613734693877551), 'median_duration_us': np.float64(1.6), 'std_dev_duration_us': np.float64(0.10155782016738636), 'min_duration_us': np.float64(1.536), 'max_duration_us': np.float64(2.176)}]</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(51.776), 'mean_duration_us': np.float64(51.776), 'median_duration_us': np.float64(51.776), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(51.776), 'max_duration_us': np.float64(51.776)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 7, 'gpu_op_uid': 11919, 'count': 1, 'total_duration_us': np.float64(51.776), 'mean_duration_us': np.float64(51.776), 'median_duration_us': np.float64(51.776), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(51.776), 'max_duration_us': np.float64(51.776)}]</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4&gt; &gt;(at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(4.128), 'mean_duration_us': np.float64(4.128), 'median_duration_us': np.float64(4.128), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.128), 'max_duration_us': np.float64(4.128)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4&gt; &gt;(at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4&gt;)', 'stream': 7, 'gpu_op_uid': 11931, 'count': 1, 'total_duration_us': np.float64(4.128), 'mean_duration_us': np.float64(4.128), 'median_duration_us': np.float64(4.128), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.128), 'max_duration_us': np.float64(4.128)}]</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_simt_sgemm_128x32_8x5_nn_align1&gt;(cutlass_80_simt_sgemm_128x32_8x5_nn_align1::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.52), 'mean_duration_us': np.float64(3.52), 'median_duration_us': np.float64(3.52), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.52), 'max_duration_us': np.float64(3.52)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_simt_sgemm_128x32_8x5_nn_align1&gt;(cutlass_80_simt_sgemm_128x32_8x5_nn_align1::Params)', 'stream': 7, 'gpu_op_uid': 11947, 'count': 1, 'total_duration_us': np.float64(3.52), 'mean_duration_us': np.float64(3.52), 'median_duration_us': np.float64(3.52), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.52), 'max_duration_us': np.float64(3.52)}]</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -12429,7 +12429,7 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.456), 'mean_duration_us': np.float64(3.456), 'median_duration_us': np.float64(3.456), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.456), 'max_duration_us': np.float64(3.456)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'gpu_op_uid': 11951, 'count': 1, 'total_duration_us': np.float64(3.456), 'mean_duration_us': np.float64(3.456), 'median_duration_us': np.float64(3.456), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.456), 'max_duration_us': np.float64(3.456)}]</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 2, 'total_duration_us': np.float64(3.136), 'mean_duration_us': np.float64(1.568), 'median_duration_us': np.float64(1.568), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.568), 'max_duration_us': np.float64(1.568)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 11963, 'count': 2, 'total_duration_us': np.float64(3.136), 'mean_duration_us': np.float64(1.568), 'median_duration_us': np.float64(1.568), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.568), 'max_duration_us': np.float64(1.568)}]</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 2, 'total_duration_us': np.float64(2.975), 'mean_duration_us': np.float64(1.4875), 'median_duration_us': np.float64(1.4875), 'std_dev_duration_us': np.float64(0.01649999999999996), 'min_duration_us': np.float64(1.471), 'max_duration_us': np.float64(1.504)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 11971, 'count': 2, 'total_duration_us': np.float64(2.975), 'mean_duration_us': np.float64(1.4875), 'median_duration_us': np.float64(1.4875), 'std_dev_duration_us': np.float64(0.01649999999999996), 'min_duration_us': np.float64(1.471), 'max_duration_us': np.float64(1.504)}]</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.592), 'mean_duration_us': np.float64(2.592), 'median_duration_us': np.float64(2.592), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.592), 'max_duration_us': np.float64(2.592)}]</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'gpu_op_uid': 11941, 'count': 1, 'total_duration_us': np.float64(2.592), 'mean_duration_us': np.float64(2.592), 'median_duration_us': np.float64(2.592), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.592), 'max_duration_us': np.float64(2.592)}]</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pinned)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.368), 'mean_duration_us': np.float64(2.368), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.368), 'max_duration_us': np.float64(2.368)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pinned)', 'stream': 7, 'gpu_op_uid': 11935, 'count': 1, 'total_duration_us': np.float64(2.368), 'mean_duration_us': np.float64(2.368), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.368), 'max_duration_us': np.float64(2.368)}]</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.08), 'mean_duration_us': np.float64(2.08), 'median_duration_us': np.float64(2.08), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.08), 'max_duration_us': np.float64(2.08)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 11955, 'count': 1, 'total_duration_us': np.float64(2.08), 'mean_duration_us': np.float64(2.08), 'median_duration_us': np.float64(2.08), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.08), 'max_duration_us': np.float64(2.08)}]</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.016), 'mean_duration_us': np.float64(2.016), 'median_duration_us': np.float64(2.016), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.016), 'max_duration_us': np.float64(2.016)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 11959, 'count': 1, 'total_duration_us': np.float64(2.016), 'mean_duration_us': np.float64(2.016), 'median_duration_us': np.float64(2.016), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.016), 'max_duration_us': np.float64(2.016)}]</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(1.856), 'mean_duration_us': np.float64(1.856), 'median_duration_us': np.float64(1.856), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.856), 'max_duration_us': np.float64(1.856)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 11927, 'count': 1, 'total_duration_us': np.float64(1.856), 'mean_duration_us': np.float64(1.856), 'median_duration_us': np.float64(1.856), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.856), 'max_duration_us': np.float64(1.856)}]</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(1.504), 'mean_duration_us': np.float64(1.504), 'median_duration_us': np.float64(1.504), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.504), 'max_duration_us': np.float64(1.504)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 7, 'gpu_op_uid': 11923, 'count': 1, 'total_duration_us': np.float64(1.504), 'mean_duration_us': np.float64(1.504), 'median_duration_us': np.float64(1.504), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.504), 'max_duration_us': np.float64(1.504)}]</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(39.75), 'mean_duration_us': np.float64(0.828125), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.07937112851450877), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.057)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(4015.5009999999997), 'mean_duration_us': np.float64(83.65627083333332), 'median_duration_us': np.float64(83.679), 'std_dev_duration_us': np.float64(1.1791844593401435), 'min_duration_us': np.float64(81.472), 'max_duration_us': np.float64(86.016)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 12177, 'count': 48, 'total_duration_us': np.float64(39.75), 'mean_duration_us': np.float64(0.828125), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.07937112851450877), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.057)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 12187, 'count': 48, 'total_duration_us': np.float64(4015.5009999999997), 'mean_duration_us': np.float64(83.65627083333332), 'median_duration_us': np.float64(83.679), 'std_dev_duration_us': np.float64(1.1791844593401435), 'min_duration_us': np.float64(81.472), 'max_duration_us': np.float64(86.016)}]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(62.783), 'mean_duration_us': np.float64(0.8719861111111111), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.11567921318307071), 'min_duration_us': np.float64(0.767), 'max_duration_us': np.float64(1.216)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(2266.292), 'mean_duration_us': np.float64(31.476277777777778), 'median_duration_us': np.float64(31.456), 'std_dev_duration_us': np.float64(0.31881400107892144), 'min_duration_us': np.float64(30.912), 'max_duration_us': np.float64(32.256)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 12013, 'count': 72, 'total_duration_us': np.float64(62.783), 'mean_duration_us': np.float64(0.8719861111111111), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.11567921318307071), 'min_duration_us': np.float64(0.767), 'max_duration_us': np.float64(1.216)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 12023, 'count': 72, 'total_duration_us': np.float64(2266.292), 'mean_duration_us': np.float64(31.476277777777778), 'median_duration_us': np.float64(31.456), 'std_dev_duration_us': np.float64(0.31881400107892144), 'min_duration_us': np.float64(30.912), 'max_duration_us': np.float64(32.256)}]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.512999999999998), 'mean_duration_us': np.float64(0.8547083333333333), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.10426427926454754), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.088)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1814.774), 'mean_duration_us': np.float64(75.61558333333333), 'median_duration_us': np.float64(75.6315), 'std_dev_duration_us': np.float64(0.4239531142184896), 'min_duration_us': np.float64(74.752), 'max_duration_us': np.float64(76.384)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 12217, 'count': 24, 'total_duration_us': np.float64(20.512999999999998), 'mean_duration_us': np.float64(0.8547083333333333), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.10426427926454754), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.088)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 12227, 'count': 24, 'total_duration_us': np.float64(1814.774), 'mean_duration_us': np.float64(75.61558333333333), 'median_duration_us': np.float64(75.6315), 'std_dev_duration_us': np.float64(0.4239531142184896), 'min_duration_us': np.float64(74.752), 'max_duration_us': np.float64(76.384)}]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -14309,7 +14309,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.001000000000005), 'mean_duration_us': np.float64(0.8333750000000002), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.08185037797713582), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.056)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(758.1399999999999), 'mean_duration_us': np.float64(31.58916666666666), 'median_duration_us': np.float64(31.552), 'std_dev_duration_us': np.float64(0.15096182372448408), 'min_duration_us': np.float64(31.392), 'max_duration_us': np.float64(31.936)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 12125, 'count': 24, 'total_duration_us': np.float64(20.001000000000005), 'mean_duration_us': np.float64(0.8333750000000002), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.08185037797713582), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.056)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 12135, 'count': 24, 'total_duration_us': np.float64(758.1399999999999), 'mean_duration_us': np.float64(31.58916666666666), 'median_duration_us': np.float64(31.552), 'std_dev_duration_us': np.float64(0.15096182372448408), 'min_duration_us': np.float64(31.392), 'max_duration_us': np.float64(31.936)}]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_simt_sgemm_128x32_8x5_nn_align1&gt;(cutlass_80_simt_sgemm_128x32_8x5_nn_align1::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.52), 'mean_duration_us': np.float64(3.52), 'median_duration_us': np.float64(3.52), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.52), 'max_duration_us': np.float64(3.52)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_simt_sgemm_128x32_8x5_nn_align1&gt;(cutlass_80_simt_sgemm_128x32_8x5_nn_align1::Params)', 'stream': 7, 'gpu_op_uid': 11947, 'count': 1, 'total_duration_us': np.float64(3.52), 'mean_duration_us': np.float64(3.52), 'median_duration_us': np.float64(3.52), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.52), 'max_duration_us': np.float64(3.52)}]</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -14855,7 +14855,7 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, true, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(2722.705), 'mean_duration_us': np.float64(113.44604166666666), 'median_duration_us': np.float64(113.775), 'std_dev_duration_us': np.float64(2.127694555913488), 'min_duration_us': np.float64(109.28), 'max_duration_us': np.float64(119.647)}]</t>
+          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, true, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'gpu_op_uid': 12115, 'count': 24, 'total_duration_us': np.float64(2722.705), 'mean_duration_us': np.float64(113.44604166666666), 'median_duration_us': np.float64(113.775), 'std_dev_duration_us': np.float64(2.127694555913488), 'min_duration_us': np.float64(109.28), 'max_duration_us': np.float64(119.647)}]</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -14919,7 +14919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL10"/>
+  <dimension ref="A1:AJ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14930,185 +14930,175 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>param: shape_in1</t>
+          <t>param: op_shape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>param: shape_in2</t>
+          <t>param: dtype_in_out</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>param: dtype_in1_in2_out</t>
+          <t>param: stride_input</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>param: stride_input1</t>
+          <t>param: stride_output</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>param: stride_input2</t>
+          <t>GFLOPS_first</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>param: stride_output</t>
+          <t>Data Moved (MB)_first</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>GFLOPS_first</t>
+          <t>FLOPS/Byte_first</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Data Moved (MB)_first</t>
+          <t>TB/s_mean</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>FLOPS/Byte_first</t>
+          <t>TB/s_median</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>TB/s_mean</t>
+          <t>TB/s_std</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>TB/s_median</t>
+          <t>TB/s_min</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>TB/s_std</t>
+          <t>TB/s_max</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>TB/s_min</t>
+          <t>TFLOPS/s_mean</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>TB/s_max</t>
+          <t>TFLOPS/s_median</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_mean</t>
+          <t>TFLOPS/s_std</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_median</t>
+          <t>TFLOPS/s_min</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_std</t>
+          <t>TFLOPS/s_max</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_min</t>
+          <t>process_name_first</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_max</t>
+          <t>process_label_first</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>process_name_first</t>
+          <t>thread_name_first</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>process_label_first</t>
+          <t>Compute Spec</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>thread_name_first</t>
+          <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Compute Spec</t>
+          <t>trunc_kernel_details</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>kernel_details__summarize_kernel_stats</t>
+          <t>Input Dims_first</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>trunc_kernel_details</t>
+          <t>Input type_first</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Input Dims_first</t>
+          <t>Input Strides_first</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Input type_first</t>
+          <t>Concrete Inputs_first</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Input Strides_first</t>
+          <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Concrete Inputs_first</t>
+          <t>Kernel Time (µs)_median</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_mean</t>
+          <t>Kernel Time (µs)_std</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_median</t>
+          <t>Kernel Time (µs)_min</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_std</t>
+          <t>Kernel Time (µs)_max</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_min</t>
+          <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_max</t>
+          <t>name_count</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_sum</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>name_count</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -15117,7 +15107,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aten::add</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -15127,12 +15117,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(16, 16, 559, 64)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+          <t>(572416, 35776, 64, 1)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15140,130 +15130,124 @@
           <t>(572416, 64, 1024, 1)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>(572416, 35776, 64, 1)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.009158655999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.9375</v>
+      </c>
       <c r="H2" t="n">
-        <v>0.009158655999999999</v>
+        <v>0.25</v>
       </c>
       <c r="I2" t="n">
-        <v>52.40625</v>
+        <v>1.251316415127883</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1.249816094217987</v>
       </c>
       <c r="K2" t="n">
-        <v>1.578555021415897</v>
+        <v>0.01381021900927246</v>
       </c>
       <c r="L2" t="n">
-        <v>1.579807895111423</v>
+        <v>1.219199524720297</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01466091314279465</v>
+        <v>1.277708976456263</v>
       </c>
       <c r="N2" t="n">
-        <v>1.542944014258392</v>
+        <v>0.3128291037819706</v>
       </c>
       <c r="O2" t="n">
-        <v>1.603453131320615</v>
+        <v>0.3124540235544968</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2630925035693162</v>
+        <v>0.003452554752318116</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2633013158519038</v>
+        <v>0.3047998811800742</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002443485523799111</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.257157335709732</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.2672421885534358</v>
+        <v>0.3194272441140658</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 25286 (python3)</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>thread 25286 (python3)</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 12099, 'count': 72, 'total_duration_us': np.float64(2108.187), 'mean_duration_us': np.float64(29.280375), 'median_duration_us': np.float64(29.312), 'std_dev_duration_us': np.float64(0.3210814381594732), 'min_duration_us': np.float64(28.672), 'max_duration_us': np.float64(30.048)}]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(29.28)}]</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(1671.096), 'mean_duration_us': np.float64(34.8145), 'median_duration_us': np.float64(34.784), 'std_dev_duration_us': np.float64(0.3216488121124247), 'min_duration_us': np.float64(34.271), 'max_duration_us': np.float64(35.615)}]</t>
+          <t>[[16, 16, 559, 64], [16, 16, 559, 64], []]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(34.81)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[[16, 16, 559, 64], [16, 16, 559, 64], []]</t>
+          <t>[[572416, 35776, 64, 1], [572416, 64, 1024, 1], []]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>[[572416, 64, 1024, 1], [572416, 35776, 64, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>['', '', '1']</t>
-        </is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>29.28038533528646</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>29.31201171875</v>
       </c>
       <c r="AE2" t="n">
-        <v>34.81449890136719</v>
+        <v>0.3233270218510627</v>
       </c>
       <c r="AF2" t="n">
-        <v>34.783935546875</v>
+        <v>28.672119140625</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3250576438614337</v>
+        <v>30.048095703125</v>
       </c>
       <c r="AH2" t="n">
-        <v>34.27099609375</v>
+        <v>2108.187744140625</v>
       </c>
       <c r="AI2" t="n">
-        <v>35.614990234375</v>
+        <v>72</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1671.095947265625</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>aten::mul</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -15273,12 +15257,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(16, 559, 1)</t>
+          <t>('float', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>('float', 'float', None)</t>
+          <t>(572416, 1024, 1)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15286,860 +15270,812 @@
           <t>(572416, 1024, 1)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>(559, 1, 1)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.009158655999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>52.40625</v>
+      </c>
       <c r="H3" t="n">
-        <v>0.009158655999999999</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="I3" t="n">
-        <v>69.90911865234375</v>
+        <v>1.881851808058028</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1249389946315276</v>
+        <v>1.880880845131154</v>
       </c>
       <c r="K3" t="n">
-        <v>2.232889871737575</v>
+        <v>0.048143115151111</v>
       </c>
       <c r="L3" t="n">
-        <v>2.24587209729754</v>
+        <v>1.828739853072367</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02901386005573873</v>
+        <v>2.176566838045875</v>
       </c>
       <c r="N3" t="n">
-        <v>2.163222010677156</v>
+        <v>0.3136419680096713</v>
       </c>
       <c r="O3" t="n">
-        <v>2.27259389729112</v>
+        <v>0.3134801408551922</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2789750156978132</v>
+        <v>0.008023852525185171</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2805970019073549</v>
+        <v>0.3047899755120612</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003624962505743834</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.2702707831787955</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.2839355967332975</v>
+        <v>0.3627611396743124</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 25286 (python3)</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_fp32</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>thread 25286 (python3)</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'gpu_op_uid': 11979, 'count': 49, 'total_duration_us': np.float64(1431.6720000000003), 'mean_duration_us': np.float64(29.21779591836735), 'median_duration_us': np.float64(29.216), 'std_dev_duration_us': np.float64(0.6654753090251477), 'min_duration_us': np.float64(25.247), 'max_duration_us': np.float64(30.049)}]</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>vector_fp32</t>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(29.22)}]</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 2, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1608.9229999999998), 'mean_duration_us': np.float64(32.835163265306115), 'median_duration_us': np.float64(32.64), 'std_dev_duration_us': np.float64(0.42625121207266925), 'min_duration_us': np.float64(32.256), 'max_duration_us': np.float64(33.887)}]</t>
+          <t>[[16, 559, 1024], [16, 559, 1024], []]</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 2, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(32.84)}]</t>
+          <t>['float', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[[16, 559, 1024], [16, 559, 1]]</t>
+          <t>[[572416, 1024, 1], [572416, 1024, 1], []]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>['float', 'float']</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>[[572416, 1024, 1], [559, 1, 1]]</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>['', '']</t>
-        </is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>29.21780333227041</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>29.216064453125</v>
       </c>
       <c r="AE3" t="n">
-        <v>32.83514528858419</v>
+        <v>0.6723608131569377</v>
       </c>
       <c r="AF3" t="n">
-        <v>32.639892578125</v>
+        <v>25.2470703125</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4306580406298848</v>
+        <v>30.049072265625</v>
       </c>
       <c r="AH3" t="n">
-        <v>32.256103515625</v>
+        <v>1431.67236328125</v>
       </c>
       <c r="AI3" t="n">
-        <v>33.886962890625</v>
+        <v>49</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1608.922119140625</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>49</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aten::mul</t>
+          <t>aten::pow</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(16, 16, 559, 64)</t>
+          <t>(16, 559, 1024)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(1, 1, 559, 64)</t>
+          <t>('float', None)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>(572416, 64, 1024, 1)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>(35776, 35776, 64, 1)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>(572416, 1024, 1)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.009158655999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>69.875</v>
+      </c>
       <c r="H4" t="n">
-        <v>0.009158655999999999</v>
+        <v>0.125</v>
       </c>
       <c r="I4" t="n">
-        <v>35.0057373046875</v>
+        <v>2.760663158867807</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2495126705653021</v>
+        <v>2.775360569367637</v>
       </c>
       <c r="K4" t="n">
-        <v>1.145799975045878</v>
+        <v>0.04288717419073364</v>
       </c>
       <c r="L4" t="n">
-        <v>1.147069145809284</v>
+        <v>2.659307593134432</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01136592585186839</v>
+        <v>2.812844702164154</v>
       </c>
       <c r="N4" t="n">
-        <v>1.123470927674201</v>
+        <v>0.3450828948584759</v>
       </c>
       <c r="O4" t="n">
-        <v>1.163354897560296</v>
+        <v>0.3469200711709545</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2858916117073536</v>
+        <v>0.005360896773841705</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2862082858939344</v>
+        <v>0.3324134491418039</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002835942512746873</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.2803202314664674</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.290271787305493</v>
+        <v>0.3516055877705191</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 25286 (python3)</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_fp32</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>thread 25286 (python3)</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 11983, 'count': 49, 'total_duration_us': np.float64(1300.7949999999998), 'mean_duration_us': np.float64(26.546836734693873), 'median_duration_us': np.float64(26.4), 'std_dev_duration_us': np.float64(0.41517418753759416), 'min_duration_us': np.float64(26.048), 'max_duration_us': np.float64(27.552)}]</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': np.float64(26.55)}]</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(1537.849), 'mean_duration_us': np.float64(32.03852083333333), 'median_duration_us': np.float64(32.0), 'std_dev_duration_us': np.float64(0.31526120054007917), 'min_duration_us': np.float64(31.552), 'max_duration_us': np.float64(32.672)}]</t>
+          <t>[[16, 559, 1024], []]</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(32.04)}]</t>
+          <t>['float', 'Scalar']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[[16, 16, 559, 64], [1, 1, 559, 64]]</t>
+          <t>[[572416, 1024, 1], []]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16']</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>[[572416, 64, 1024, 1], [35776, 35776, 64, 1]]</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>['', '']</t>
-        </is>
+          <t>['', '2']</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>26.54683514030612</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>26.39990234375</v>
       </c>
       <c r="AE4" t="n">
-        <v>32.03850809733073</v>
+        <v>0.4194831695891557</v>
       </c>
       <c r="AF4" t="n">
-        <v>32</v>
+        <v>26.048095703125</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3186166119751925</v>
+        <v>27.552001953125</v>
       </c>
       <c r="AH4" t="n">
-        <v>31.552001953125</v>
+        <v>1300.794921875</v>
       </c>
       <c r="AI4" t="n">
-        <v>32.672119140625</v>
+        <v>49</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1537.848388671875</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>123</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>aten::mul</t>
+          <t>aten::silu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(1024,)</t>
+          <t>(16, 559, 2816)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(16, 559, 1024)</t>
+          <t>('c10::BFloat16', None)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(1,)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>(572416, 1024, 1)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>(1574144, 2816, 1)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.025186304</v>
+      </c>
+      <c r="G5" t="n">
+        <v>96.078125</v>
+      </c>
       <c r="H5" t="n">
-        <v>0.009158655999999999</v>
+        <v>0.25</v>
       </c>
       <c r="I5" t="n">
-        <v>34.939453125</v>
+        <v>2.613825645550667</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2499860249315222</v>
+        <v>2.622488354030101</v>
       </c>
       <c r="K5" t="n">
-        <v>1.455153399255028</v>
+        <v>0.02440290095124216</v>
       </c>
       <c r="L5" t="n">
-        <v>1.460332897158427</v>
+        <v>2.565847379051764</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02268735484717277</v>
+        <v>2.641178232798679</v>
       </c>
       <c r="N5" t="n">
-        <v>1.401339190108884</v>
+        <v>0.6534564113876667</v>
       </c>
       <c r="O5" t="n">
-        <v>1.490754383557017</v>
+        <v>0.6556220885075253</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3637680139453567</v>
+        <v>0.006100725237810539</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3650628160373686</v>
+        <v>0.6414618447629411</v>
       </c>
       <c r="R5" t="n">
-        <v>0.005671521654455616</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.3503152137160786</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.3726677624946603</v>
+        <v>0.6602945581996698</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 25286 (python3)</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>thread 25286 (python3)</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 12191, 'count': 24, 'total_duration_us': np.float64(925.115), 'mean_duration_us': np.float64(38.546458333333334), 'median_duration_us': np.float64(38.416), 'std_dev_duration_us': np.float64(0.35488331171042203), 'min_duration_us': np.float64(38.144), 'max_duration_us': np.float64(39.264)}]</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': np.float64(38.55)}]</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1233.979), 'mean_duration_us': np.float64(25.183244897959185), 'median_duration_us': np.float64(25.088), 'std_dev_duration_us': np.float64(0.3931505673357448), 'min_duration_us': np.float64(24.576), 'max_duration_us': np.float64(26.144)}]</t>
+          <t>[[16, 559, 2816]]</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(25.18)}]</t>
+          <t>['c10::BFloat16']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[[1024], [16, 559, 1024]]</t>
+          <t>[[1574144, 2816, 1]]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16']</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>[[1], [572416, 1024, 1]]</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>['', '']</t>
-        </is>
+          <t>['']</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>38.54644775390625</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>38.4158935546875</v>
       </c>
       <c r="AE5" t="n">
-        <v>25.18325494260204</v>
+        <v>0.3625162870903211</v>
       </c>
       <c r="AF5" t="n">
-        <v>25.087890625</v>
+        <v>38.14404296875</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3972371439579201</v>
+        <v>39.263916015625</v>
       </c>
       <c r="AH5" t="n">
-        <v>24.575927734375</v>
+        <v>925.11474609375</v>
       </c>
       <c r="AI5" t="n">
-        <v>26.14404296875</v>
+        <v>24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1233.9794921875</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>49</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>82</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aten::mul</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(16, 559, 2816)</t>
+          <t>(16, 559, 1024)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(16, 559, 2816)</t>
+          <t>('c10::BFloat16', 'float')</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+          <t>(572416, 1024, 1)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(1574144, 2816, 1)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>(1574144, 2816, 1)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>(572416, 1024, 1)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.009158655999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>52.40625</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.025186304</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="I6" t="n">
-        <v>144.1171875</v>
+        <v>2.998193462563624</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1666666666666667</v>
+        <v>3.012717402470855</v>
       </c>
       <c r="K6" t="n">
-        <v>2.955965918518416</v>
+        <v>0.05798757085308172</v>
       </c>
       <c r="L6" t="n">
-        <v>2.958964947487535</v>
+        <v>2.815157838957401</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03648177305829473</v>
+        <v>3.077681103946181</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9008140701562</v>
+        <v>0.4996989104272707</v>
       </c>
       <c r="O6" t="n">
-        <v>3.011753577999329</v>
+        <v>0.5021195670784757</v>
       </c>
       <c r="P6" t="n">
-        <v>0.492660986419736</v>
+        <v>0.009664595142180274</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4931608245812559</v>
+        <v>0.4691929731595667</v>
       </c>
       <c r="R6" t="n">
-        <v>0.006080295509715772</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.4834690116927</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.5019589296665548</v>
+        <v>0.5129468506576967</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 25286 (python3)</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>thread 25286 (python3)</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 12003, 'count': 49, 'total_duration_us': np.float64(898.427), 'mean_duration_us': np.float64(18.335244897959186), 'median_duration_us': np.float64(18.24), 'std_dev_duration_us': np.float64(0.36088720215331926), 'min_duration_us': np.float64(17.855), 'max_duration_us': np.float64(19.52)}]</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 7, 'mean_duration_us': np.float64(18.34)}]</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1227.131), 'mean_duration_us': np.float64(51.13045833333334), 'median_duration_us': np.float64(51.072), 'std_dev_duration_us': np.float64(0.617469161117019), 'min_duration_us': np.float64(50.176), 'max_duration_us': np.float64(52.095)}]</t>
+          <t>[[16, 559, 1024], [16, 559, 1024], []]</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(51.13)}]</t>
+          <t>['c10::BFloat16', 'float', 'Scalar']</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>[[16, 559, 2816], [16, 559, 2816]]</t>
+          <t>[[572416, 1024, 1], [572416, 1024, 1], []]</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16']</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>[[1574144, 2816, 1], [1574144, 2816, 1]]</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>['', '']</t>
-        </is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>18.33525490274235</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>18.239990234375</v>
       </c>
       <c r="AE6" t="n">
-        <v>51.13045247395834</v>
+        <v>0.3646247760047354</v>
       </c>
       <c r="AF6" t="n">
-        <v>51.0718994140625</v>
+        <v>17.85498046875</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.6307408003200445</v>
+        <v>19.52001953125</v>
       </c>
       <c r="AH6" t="n">
-        <v>50.176025390625</v>
+        <v>898.427490234375</v>
       </c>
       <c r="AI6" t="n">
-        <v>52.094970703125</v>
+        <v>49</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1227.130859375</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>227</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aten::mul</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(16, 16, 559, 64)</t>
+          <t>(16, 559, 16, 64)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(1, 1, 559, 64)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+          <t>(572416, 1024, 64, 1)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(572416, 35776, 64, 1)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>(35776, 35776, 64, 1)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>(572416, 64, 35776, 1)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.009158655999999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>34.9375</v>
+      </c>
       <c r="H7" t="n">
-        <v>0.009158655999999999</v>
+        <v>0.25</v>
       </c>
       <c r="I7" t="n">
-        <v>35.0057373046875</v>
+        <v>1.33614195325411</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2495126705653021</v>
+        <v>1.334300372612484</v>
       </c>
       <c r="K7" t="n">
-        <v>1.543063620342586</v>
+        <v>0.01108204259362011</v>
       </c>
       <c r="L7" t="n">
-        <v>1.543840971967223</v>
+        <v>1.314384743912267</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01180905278082167</v>
+        <v>1.361219745854349</v>
       </c>
       <c r="N7" t="n">
-        <v>1.507313545365228</v>
+        <v>0.3340354883135274</v>
       </c>
       <c r="O7" t="n">
-        <v>1.569170443734736</v>
+        <v>0.3335750931531211</v>
       </c>
       <c r="P7" t="n">
-        <v>0.385013924763842</v>
+        <v>0.002770510648405019</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3852078838436736</v>
+        <v>0.3285961859780666</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002946508296189431</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.3760938280833316</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.3915279079883942</v>
+        <v>0.3403049364635872</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 25286 (python3)</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>thread 25286 (python3)</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 12119, 'count': 24, 'total_duration_us': np.float64(658.0799999999999), 'mean_duration_us': np.float64(27.419999999999998), 'median_duration_us': np.float64(27.456), 'std_dev_duration_us': np.float64(0.2218289506203673), 'min_duration_us': np.float64(26.913), 'max_duration_us': np.float64(27.872)}]</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(27.42)}]</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(1141.883), 'mean_duration_us': np.float64(23.78922916666667), 'median_duration_us': np.float64(23.776), 'std_dev_duration_us': np.float64(0.18074236263063953), 'min_duration_us': np.float64(23.392), 'max_duration_us': np.float64(24.352)}]</t>
+          <t>[[16, 559, 16, 64], [16, 559, 16, 64], []]</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(23.79)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>[[16, 16, 559, 64], [1, 1, 559, 64]]</t>
+          <t>[[572416, 1024, 64, 1], [572416, 64, 35776, 1], []]</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16']</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>[[572416, 35776, 64, 1], [35776, 35776, 64, 1]]</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>['', '']</t>
-        </is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>27.42001342773438</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>27.4560546875</v>
       </c>
       <c r="AE7" t="n">
-        <v>23.78922526041667</v>
+        <v>0.2265912406627222</v>
       </c>
       <c r="AF7" t="n">
-        <v>23.77587890625</v>
+        <v>26.9130859375</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.1826717306685092</v>
+        <v>27.8720703125</v>
       </c>
       <c r="AH7" t="n">
-        <v>23.39208984375</v>
+        <v>658.080322265625</v>
       </c>
       <c r="AI7" t="n">
-        <v>24.35205078125</v>
+        <v>24</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1141.8828125</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>130</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aten::add</t>
+          <t>aten::neg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(16, 559, 1024)</t>
+          <t>(16, 16, 559, 32)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(16, 559, 1024)</t>
+          <t>('c10::BFloat16', None)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>(572416, 1024, 1)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>(572416, 1024, 1)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>(572416, 64, 1024, 1)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.004579328</v>
+      </c>
+      <c r="G8" t="n">
+        <v>17.46875</v>
+      </c>
       <c r="H8" t="n">
-        <v>0.009158655999999999</v>
+        <v>0.25</v>
       </c>
       <c r="I8" t="n">
-        <v>52.40625</v>
+        <v>1.498114585099769</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1666666666666667</v>
+        <v>1.502417196363491</v>
       </c>
       <c r="K8" t="n">
-        <v>3.088961333915809</v>
+        <v>0.04096435731401789</v>
       </c>
       <c r="L8" t="n">
-        <v>3.077512782083186</v>
+        <v>1.379312619762846</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08968722206012</v>
+        <v>1.576908088694592</v>
       </c>
       <c r="N8" t="n">
-        <v>2.890981284354651</v>
+        <v>0.3745286462749423</v>
       </c>
       <c r="O8" t="n">
-        <v>3.221870998926439</v>
+        <v>0.3756042990908726</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5148268889859681</v>
+        <v>0.01024108932850447</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5129187970138642</v>
+        <v>0.3448281549407115</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01494787034335336</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.4818302140591083</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.5369784998210732</v>
+        <v>0.394227022173648</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 25286 (python3)</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>thread 25286 (python3)</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 12063, 'count': 48, 'total_duration_us': np.float64(587.328), 'mean_duration_us': np.float64(12.235999999999999), 'median_duration_us': np.float64(12.192), 'std_dev_duration_us': np.float64(0.3355813363900522), 'min_duration_us': np.float64(11.616), 'max_duration_us': np.float64(13.28)}]</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(12.24)}]</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(854.619), 'mean_duration_us': np.float64(17.8045625), 'median_duration_us': np.float64(17.856), 'std_dev_duration_us': np.float64(0.5150970744371872), 'min_duration_us': np.float64(17.056), 'max_duration_us': np.float64(19.008)}]</t>
+          <t>[[16, 16, 559, 32]]</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(17.8)}]</t>
+          <t>['c10::BFloat16']</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>[[16, 559, 1024], [16, 559, 1024], []]</t>
+          <t>[[572416, 64, 1024, 1]]</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>[[572416, 1024, 1], [572416, 1024, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>['', '', '1']</t>
-        </is>
+          <t>['']</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>12.23598225911458</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>12.19189453125</v>
       </c>
       <c r="AE8" t="n">
-        <v>17.80457051595052</v>
+        <v>0.339127372422647</v>
       </c>
       <c r="AF8" t="n">
-        <v>17.85595703125</v>
+        <v>11.615966796875</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.5205274181052388</v>
+        <v>13.280029296875</v>
       </c>
       <c r="AH8" t="n">
-        <v>17.055908203125</v>
+        <v>587.3271484375</v>
       </c>
       <c r="AI8" t="n">
-        <v>19.008056640625</v>
+        <v>48</v>
       </c>
       <c r="AJ8" t="n">
-        <v>854.619384765625</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>191</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>aten::add</t>
+          <t>aten::rsqrt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -16149,143 +16085,133 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>()</t>
+          <t>('float', None)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>('float', 'double', None)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
           <t>(559, 1, 1)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>8.943999999999999e-06</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0682373046875</v>
+      </c>
       <c r="H9" t="n">
-        <v>8.943999999999999e-06</v>
+        <v>0.125</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06824493408203125</v>
+        <v>0.04448198949629482</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1249860257126887</v>
+        <v>0.04471727067439732</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04296483270099744</v>
+        <v>0.002337396261609372</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04384588780852655</v>
+        <v>0.03288196925838663</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002019140884211925</v>
+        <v>0.04658670990303609</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03666163352095059</v>
+        <v>0.005560248687036851</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04563440137007629</v>
+        <v>0.005589658834299664</v>
       </c>
       <c r="P9" t="n">
-        <v>0.005370003684708232</v>
+        <v>0.0002921745327011712</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.005480123261032161</v>
+        <v>0.004110246157298328</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0002523643944716527</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.004582191869918698</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.005703662463023508</v>
+        <v>0.00582333873787951</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 25286 (python3)</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_fp32</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>thread 25286 (python3)</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 11995, 'count': 49, 'total_duration_us': np.float64(79.073), 'mean_duration_us': np.float64(1.613734693877551), 'median_duration_us': np.float64(1.6), 'std_dev_duration_us': np.float64(0.10155782016738636), 'min_duration_us': np.float64(1.536), 'max_duration_us': np.float64(2.176)}]</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>vector_fp32</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::rs...', 'stream': 7, 'mean_duration_us': np.float64(1.61)}]</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(81.797), 'mean_duration_us': np.float64(1.669326530612245), 'median_duration_us': np.float64(1.632), 'std_dev_duration_us': np.float64(0.08264514449362109), 'min_duration_us': np.float64(1.568), 'max_duration_us': np.float64(1.952)}]</t>
+          <t>[[16, 559, 1]]</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.67)}]</t>
+          <t>['float']</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>[[16, 559, 1], [], []]</t>
+          <t>[[559, 1, 1]]</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>['float', 'double', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>[[559, 1, 1], [], []]</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>['', '', '1']</t>
-        </is>
+          <t>['']</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.613804408482143</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.60009765625</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.669383769132653</v>
+        <v>0.1026021369823694</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.632080078125</v>
+        <v>1.535888671875</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0834552892669608</v>
+        <v>2.176025390625</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.568115234375</v>
+        <v>79.076416015625</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.951904296875</v>
+        <v>49</v>
       </c>
       <c r="AJ9" t="n">
-        <v>81.7998046875</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>49</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>aten::mul</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -16295,12 +16221,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>()</t>
+          <t>('c10::BFloat16', 'float')</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>('float', 'double', None)</t>
+          <t>(35776, 64, 1)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -16308,124 +16234,252 @@
           <t>(35776, 64, 1)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>3.5776e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2047119140625</v>
+      </c>
       <c r="H10" t="n">
-        <v>3.5776e-05</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2729568481445312</v>
+        <v>0.1443313768734171</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1249965061352265</v>
+        <v>0.1443313768734171</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1825223004826405</v>
+        <v>0.002261434365022539</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1825223004826405</v>
+        <v>0.1427323012987013</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.1459304524481328</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1825223004826405</v>
+        <v>0.02405522947890284</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1825223004826405</v>
+        <v>0.02405522947890284</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02281464985209403</v>
+        <v>0.0003769057275037565</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.02281464985209403</v>
+        <v>0.02378871688311688</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.02281464985209403</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.02281464985209403</v>
+        <v>0.02432174207468879</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>thread 25286 (python3)</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 11971, 'count': 2, 'total_duration_us': np.float64(2.975), 'mean_duration_us': np.float64(1.4875), 'median_duration_us': np.float64(1.4875), 'std_dev_duration_us': np.float64(0.01649999999999996), 'min_duration_us': np.float64(1.471), 'max_duration_us': np.float64(1.504)}]</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 7, 'mean_duration_us': np.float64(1.49)}]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>[[1, 559, 64], [1, 559, 64], []]</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'float', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>[[35776, 64, 1], [35776, 64, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.4874267578125</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.4874267578125</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.02330552135258396</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.470947265625</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.50390625</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.974853515625</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>(1, 1, 559)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>('float', 'long int')</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>(559, 559, 1)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>(559, 559, 1)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>5.59e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.006397247314453125</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.00258792201186776</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.00258792201186776</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0.00258792201186776</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.00258792201186776</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0002156601676556466</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0002156601676556466</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>0.0002156601676556466</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.0002156601676556466</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>thread 25286 (python3)</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>vector_fp32</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 2, 'total_duration_us': np.float64(3.136), 'mean_duration_us': np.float64(1.568), 'median_duration_us': np.float64(1.568), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.568), 'max_duration_us': np.float64(1.568)}]</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(1.57)}]</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>[[1, 559, 64], []]</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>['float', 'double']</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>[[35776, 64, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>['', '']</t>
-        </is>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.568115234375</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.568115234375</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.568115234375</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.568115234375</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>3.13623046875</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>57</v>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'gpu_op_uid': 11941, 'count': 1, 'total_duration_us': np.float64(2.592), 'mean_duration_us': np.float64(2.592), 'median_duration_us': np.float64(2.592), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.592), 'max_duration_us': np.float64(2.592)}]</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(2.59)}]</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>[[1, 1, 559], [1, 1, 559], []]</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>['float', 'long int', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>[[559, 559, 1], [559, 559, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.592041015625</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.592041015625</v>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="n">
+        <v>2.592041015625</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.592041015625</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.592041015625</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -16439,7 +16493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16450,175 +16504,185 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>param: op_shape</t>
+          <t>param: shape_in1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>param: dtype_in_out</t>
+          <t>param: shape_in2</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>param: stride_input</t>
+          <t>param: dtype_in1_in2_out</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>param: stride_input1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>param: stride_input2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>param: stride_output</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -16627,7 +16691,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::add</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -16637,137 +16701,143 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>(16, 16, 559, 64)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>(572416, 64, 1024, 1)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>(572416, 35776, 64, 1)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>(572416, 64, 1024, 1)</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
         <v>0.009158655999999999</v>
       </c>
-      <c r="G2" t="n">
-        <v>34.9375</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I2" t="n">
-        <v>1.251316415127883</v>
+        <v>52.40625</v>
       </c>
       <c r="J2" t="n">
-        <v>1.249816094217987</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01381021900927246</v>
+        <v>1.578555021415897</v>
       </c>
       <c r="L2" t="n">
-        <v>1.219199524720297</v>
+        <v>1.579807895111423</v>
       </c>
       <c r="M2" t="n">
-        <v>1.277708976456263</v>
+        <v>0.01466091314279465</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3128291037819706</v>
+        <v>1.542944014258392</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3124540235544968</v>
+        <v>1.603453131320615</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003452554752318116</v>
+        <v>0.2630925035693162</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3047998811800742</v>
+        <v>0.2633013158519038</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3194272441140658</v>
-      </c>
-      <c r="S2" t="inlineStr">
+        <v>0.002443485523799111</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.257157335709732</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.2672421885534358</v>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>thread 25286 (python3)</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(2108.187), 'mean_duration_us': np.float64(29.280375), 'median_duration_us': np.float64(29.312), 'std_dev_duration_us': np.float64(0.3210814381594732), 'min_duration_us': np.float64(28.672), 'max_duration_us': np.float64(30.048)}]</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(29.28)}]</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 12075, 'count': 48, 'total_duration_us': np.float64(1671.096), 'mean_duration_us': np.float64(34.8145), 'median_duration_us': np.float64(34.784), 'std_dev_duration_us': np.float64(0.3216488121124247), 'min_duration_us': np.float64(34.271), 'max_duration_us': np.float64(35.615)}]</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(34.81)}]</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>[[16, 16, 559, 64], [16, 16, 559, 64], []]</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>[[572416, 35776, 64, 1], [572416, 64, 1024, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC2" t="n">
-        <v>29.28038533528646</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>29.31201171875</v>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>[[572416, 64, 1024, 1], [572416, 35776, 64, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>['', '', '1']</t>
+        </is>
       </c>
       <c r="AE2" t="n">
-        <v>0.3233270218510627</v>
+        <v>34.81449890136719</v>
       </c>
       <c r="AF2" t="n">
-        <v>28.672119140625</v>
+        <v>34.783935546875</v>
       </c>
       <c r="AG2" t="n">
-        <v>30.048095703125</v>
+        <v>0.3250576438614337</v>
       </c>
       <c r="AH2" t="n">
-        <v>2108.187744140625</v>
+        <v>34.27099609375</v>
       </c>
       <c r="AI2" t="n">
-        <v>72</v>
+        <v>35.614990234375</v>
       </c>
       <c r="AJ2" t="n">
-        <v>145</v>
+        <v>1671.095947265625</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>131</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::mul</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -16777,825 +16847,873 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>('float', 'c10::BFloat16')</t>
+          <t>(16, 559, 1)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>('float', 'float', None)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>(572416, 1024, 1)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>(572416, 1024, 1)</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(559, 1, 1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>0.009158655999999999</v>
       </c>
-      <c r="G3" t="n">
-        <v>52.40625</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
       <c r="I3" t="n">
-        <v>1.881851808058028</v>
+        <v>69.90911865234375</v>
       </c>
       <c r="J3" t="n">
-        <v>1.880880845131154</v>
+        <v>0.1249389946315276</v>
       </c>
       <c r="K3" t="n">
-        <v>0.048143115151111</v>
+        <v>2.232889871737575</v>
       </c>
       <c r="L3" t="n">
-        <v>1.828739853072367</v>
+        <v>2.24587209729754</v>
       </c>
       <c r="M3" t="n">
-        <v>2.176566838045875</v>
+        <v>0.02901386005573873</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3136419680096713</v>
+        <v>2.163222010677156</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3134801408551922</v>
+        <v>2.27259389729112</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008023852525185171</v>
+        <v>0.2789750156978132</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3047899755120612</v>
+        <v>0.2805970019073549</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3627611396743124</v>
-      </c>
-      <c r="S3" t="inlineStr">
+        <v>0.003624962505743834</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2702707831787955</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.2839355967332975</v>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>thread 25286 (python3)</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>vector_fp32</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1431.6720000000003), 'mean_duration_us': np.float64(29.21779591836735), 'median_duration_us': np.float64(29.216), 'std_dev_duration_us': np.float64(0.6654753090251477), 'min_duration_us': np.float64(25.247), 'max_duration_us': np.float64(30.049)}]</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(29.22)}]</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[[16, 559, 1024], [16, 559, 1024], []]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 2, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 11999, 'count': 49, 'total_duration_us': np.float64(1608.9229999999998), 'mean_duration_us': np.float64(32.835163265306115), 'median_duration_us': np.float64(32.64), 'std_dev_duration_us': np.float64(0.42625121207266925), 'min_duration_us': np.float64(32.256), 'max_duration_us': np.float64(33.887)}]</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>['float', 'c10::BFloat16', 'Scalar']</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 2, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(32.84)}]</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[[572416, 1024, 1], [572416, 1024, 1], []]</t>
+          <t>[[16, 559, 1024], [16, 559, 1]]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>29.21780333227041</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>29.216064453125</v>
+          <t>['float', 'float']</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>[[572416, 1024, 1], [559, 1, 1]]</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>['', '']</t>
+        </is>
       </c>
       <c r="AE3" t="n">
-        <v>0.6723608131569377</v>
+        <v>32.83514528858419</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.2470703125</v>
+        <v>32.639892578125</v>
       </c>
       <c r="AG3" t="n">
-        <v>30.049072265625</v>
+        <v>0.4306580406298848</v>
       </c>
       <c r="AH3" t="n">
-        <v>1431.67236328125</v>
+        <v>32.256103515625</v>
       </c>
       <c r="AI3" t="n">
+        <v>33.886962890625</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1608.922119140625</v>
+      </c>
+      <c r="AK3" t="n">
         <v>49</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>70</v>
+      <c r="AL3" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aten::pow</t>
+          <t>aten::mul</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(16, 559, 1024)</t>
+          <t>(16, 16, 559, 64)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>('float', None)</t>
+          <t>(1, 1, 559, 64)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(572416, 1024, 1)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>(572416, 64, 1024, 1)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(35776, 35776, 64, 1)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>0.009158655999999999</v>
       </c>
-      <c r="G4" t="n">
-        <v>69.875</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.125</v>
-      </c>
       <c r="I4" t="n">
-        <v>2.760663158867807</v>
+        <v>35.0057373046875</v>
       </c>
       <c r="J4" t="n">
-        <v>2.775360569367637</v>
+        <v>0.2495126705653021</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04288717419073364</v>
+        <v>1.145799975045878</v>
       </c>
       <c r="L4" t="n">
-        <v>2.659307593134432</v>
+        <v>1.147069145809284</v>
       </c>
       <c r="M4" t="n">
-        <v>2.812844702164154</v>
+        <v>0.01136592585186839</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3450828948584759</v>
+        <v>1.123470927674201</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3469200711709545</v>
+        <v>1.163354897560296</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005360896773841705</v>
+        <v>0.2858916117073536</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3324134491418039</v>
+        <v>0.2862082858939344</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3516055877705191</v>
-      </c>
-      <c r="S4" t="inlineStr">
+        <v>0.002835942512746873</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.2803202314664674</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.290271787305493</v>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>thread 25286 (python3)</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>vector_fp32</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1300.7949999999998), 'mean_duration_us': np.float64(26.546836734693873), 'median_duration_us': np.float64(26.4), 'std_dev_duration_us': np.float64(0.41517418753759416), 'min_duration_us': np.float64(26.048), 'max_duration_us': np.float64(27.552)}]</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': np.float64(26.55)}]</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[[16, 559, 1024], []]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 12059, 'count': 48, 'total_duration_us': np.float64(1537.849), 'mean_duration_us': np.float64(32.03852083333333), 'median_duration_us': np.float64(32.0), 'std_dev_duration_us': np.float64(0.31526120054007917), 'min_duration_us': np.float64(31.552), 'max_duration_us': np.float64(32.672)}]</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>['float', 'Scalar']</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(32.04)}]</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[[572416, 1024, 1], []]</t>
+          <t>[[16, 16, 559, 64], [1, 1, 559, 64]]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>['', '2']</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>26.54683514030612</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>26.39990234375</v>
+          <t>['c10::BFloat16', 'c10::BFloat16']</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>[[572416, 64, 1024, 1], [35776, 35776, 64, 1]]</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>['', '']</t>
+        </is>
       </c>
       <c r="AE4" t="n">
-        <v>0.4194831695891557</v>
+        <v>32.03850809733073</v>
       </c>
       <c r="AF4" t="n">
-        <v>26.048095703125</v>
+        <v>32</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.552001953125</v>
+        <v>0.3186166119751925</v>
       </c>
       <c r="AH4" t="n">
-        <v>1300.794921875</v>
+        <v>31.552001953125</v>
       </c>
       <c r="AI4" t="n">
-        <v>49</v>
+        <v>32.672119140625</v>
       </c>
       <c r="AJ4" t="n">
-        <v>71</v>
+        <v>1537.848388671875</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>123</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>aten::silu</t>
+          <t>aten::mul</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(16, 559, 2816)</t>
+          <t>(1024,)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', None)</t>
+          <t>(16, 559, 1024)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(1574144, 2816, 1)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>0.025186304</v>
-      </c>
-      <c r="G5" t="n">
-        <v>96.078125</v>
-      </c>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(1,)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>(572416, 1024, 1)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.25</v>
+        <v>0.009158655999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>2.613825645550667</v>
+        <v>34.939453125</v>
       </c>
       <c r="J5" t="n">
-        <v>2.622488354030101</v>
+        <v>0.2499860249315222</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02440290095124216</v>
+        <v>1.455153399255028</v>
       </c>
       <c r="L5" t="n">
-        <v>2.565847379051764</v>
+        <v>1.460332897158427</v>
       </c>
       <c r="M5" t="n">
-        <v>2.641178232798679</v>
+        <v>0.02268735484717277</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6534564113876667</v>
+        <v>1.401339190108884</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6556220885075253</v>
+        <v>1.490754383557017</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006100725237810539</v>
+        <v>0.3637680139453567</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6414618447629411</v>
+        <v>0.3650628160373686</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6602945581996698</v>
-      </c>
-      <c r="S5" t="inlineStr">
+        <v>0.005671521654455616</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3503152137160786</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.3726677624946603</v>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>thread 25286 (python3)</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(925.115), 'mean_duration_us': np.float64(38.546458333333334), 'median_duration_us': np.float64(38.416), 'std_dev_duration_us': np.float64(0.35488331171042203), 'min_duration_us': np.float64(38.144), 'max_duration_us': np.float64(39.264)}]</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': np.float64(38.55)}]</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[[16, 559, 2816]]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 12007, 'count': 49, 'total_duration_us': np.float64(1233.979), 'mean_duration_us': np.float64(25.183244897959185), 'median_duration_us': np.float64(25.088), 'std_dev_duration_us': np.float64(0.3931505673357448), 'min_duration_us': np.float64(24.576), 'max_duration_us': np.float64(26.144)}]</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>['c10::BFloat16']</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(25.18)}]</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[[1574144, 2816, 1]]</t>
+          <t>[[1024], [16, 559, 1024]]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>['']</t>
-        </is>
-      </c>
-      <c r="AC5" t="n">
-        <v>38.54644775390625</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>38.4158935546875</v>
+          <t>['c10::BFloat16', 'c10::BFloat16']</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>[[1], [572416, 1024, 1]]</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>['', '']</t>
+        </is>
       </c>
       <c r="AE5" t="n">
-        <v>0.3625162870903211</v>
+        <v>25.18325494260204</v>
       </c>
       <c r="AF5" t="n">
-        <v>38.14404296875</v>
+        <v>25.087890625</v>
       </c>
       <c r="AG5" t="n">
-        <v>39.263916015625</v>
+        <v>0.3972371439579201</v>
       </c>
       <c r="AH5" t="n">
-        <v>925.11474609375</v>
+        <v>24.575927734375</v>
       </c>
       <c r="AI5" t="n">
-        <v>24</v>
+        <v>26.14404296875</v>
       </c>
       <c r="AJ5" t="n">
-        <v>217</v>
+        <v>1233.9794921875</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>49</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::mul</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(16, 559, 1024)</t>
+          <t>(16, 559, 2816)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'float')</t>
+          <t>(16, 559, 2816)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(572416, 1024, 1)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(572416, 1024, 1)</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.009158655999999999</v>
-      </c>
-      <c r="G6" t="n">
-        <v>52.40625</v>
-      </c>
+          <t>(1574144, 2816, 1)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>(1574144, 2816, 1)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
+        <v>0.025186304</v>
+      </c>
+      <c r="I6" t="n">
+        <v>144.1171875</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="I6" t="n">
-        <v>2.998193462563624</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.012717402470855</v>
-      </c>
       <c r="K6" t="n">
-        <v>0.05798757085308172</v>
+        <v>2.955965918518416</v>
       </c>
       <c r="L6" t="n">
-        <v>2.815157838957401</v>
+        <v>2.958964947487535</v>
       </c>
       <c r="M6" t="n">
-        <v>3.077681103946181</v>
+        <v>0.03648177305829473</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4996989104272707</v>
+        <v>2.9008140701562</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5021195670784757</v>
+        <v>3.011753577999329</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009664595142180274</v>
+        <v>0.492660986419736</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4691929731595667</v>
+        <v>0.4931608245812559</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5129468506576967</v>
-      </c>
-      <c r="S6" t="inlineStr">
+        <v>0.006080295509715772</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.4834690116927</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.5019589296665548</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>thread 25286 (python3)</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(898.427), 'mean_duration_us': np.float64(18.335244897959186), 'median_duration_us': np.float64(18.24), 'std_dev_duration_us': np.float64(0.36088720215331926), 'min_duration_us': np.float64(17.855), 'max_duration_us': np.float64(19.52)}]</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 7, 'mean_duration_us': np.float64(18.34)}]</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[[16, 559, 1024], [16, 559, 1024], []]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'gpu_op_uid': 12211, 'count': 24, 'total_duration_us': np.float64(1227.131), 'mean_duration_us': np.float64(51.13045833333334), 'median_duration_us': np.float64(51.072), 'std_dev_duration_us': np.float64(0.617469161117019), 'min_duration_us': np.float64(50.176), 'max_duration_us': np.float64(52.095)}]</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'float', 'Scalar']</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(51.13)}]</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>[[572416, 1024, 1], [572416, 1024, 1], []]</t>
+          <t>[[16, 559, 2816], [16, 559, 2816]]</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC6" t="n">
-        <v>18.33525490274235</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>18.239990234375</v>
+          <t>['c10::BFloat16', 'c10::BFloat16']</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>[[1574144, 2816, 1], [1574144, 2816, 1]]</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>['', '']</t>
+        </is>
       </c>
       <c r="AE6" t="n">
-        <v>0.3646247760047354</v>
+        <v>51.13045247395834</v>
       </c>
       <c r="AF6" t="n">
-        <v>17.85498046875</v>
+        <v>51.0718994140625</v>
       </c>
       <c r="AG6" t="n">
-        <v>19.52001953125</v>
+        <v>0.6307408003200445</v>
       </c>
       <c r="AH6" t="n">
-        <v>898.427490234375</v>
+        <v>50.176025390625</v>
       </c>
       <c r="AI6" t="n">
-        <v>49</v>
+        <v>52.094970703125</v>
       </c>
       <c r="AJ6" t="n">
-        <v>81</v>
+        <v>1227.130859375</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>227</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::mul</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(16, 559, 16, 64)</t>
+          <t>(16, 16, 559, 64)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>(1, 1, 559, 64)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(572416, 1024, 64, 1)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(572416, 64, 35776, 1)</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+          <t>(572416, 35776, 64, 1)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>(35776, 35776, 64, 1)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>0.009158655999999999</v>
       </c>
-      <c r="G7" t="n">
-        <v>34.9375</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I7" t="n">
-        <v>1.33614195325411</v>
+        <v>35.0057373046875</v>
       </c>
       <c r="J7" t="n">
-        <v>1.334300372612484</v>
+        <v>0.2495126705653021</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01108204259362011</v>
+        <v>1.543063620342586</v>
       </c>
       <c r="L7" t="n">
-        <v>1.314384743912267</v>
+        <v>1.543840971967223</v>
       </c>
       <c r="M7" t="n">
-        <v>1.361219745854349</v>
+        <v>0.01180905278082167</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3340354883135274</v>
+        <v>1.507313545365228</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3335750931531211</v>
+        <v>1.569170443734736</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002770510648405019</v>
+        <v>0.385013924763842</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3285961859780666</v>
+        <v>0.3852078838436736</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3403049364635872</v>
-      </c>
-      <c r="S7" t="inlineStr">
+        <v>0.002946508296189431</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3760938280833316</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.3915279079883942</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>thread 25286 (python3)</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(658.0799999999999), 'mean_duration_us': np.float64(27.419999999999998), 'median_duration_us': np.float64(27.456), 'std_dev_duration_us': np.float64(0.2218289506203673), 'min_duration_us': np.float64(26.913), 'max_duration_us': np.float64(27.872)}]</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(27.42)}]</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[[16, 559, 16, 64], [16, 559, 16, 64], []]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 12071, 'count': 48, 'total_duration_us': np.float64(1141.883), 'mean_duration_us': np.float64(23.78922916666667), 'median_duration_us': np.float64(23.776), 'std_dev_duration_us': np.float64(0.18074236263063953), 'min_duration_us': np.float64(23.392), 'max_duration_us': np.float64(24.352)}]</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(23.79)}]</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>[[572416, 1024, 64, 1], [572416, 64, 35776, 1], []]</t>
+          <t>[[16, 16, 559, 64], [1, 1, 559, 64]]</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC7" t="n">
-        <v>27.42001342773438</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>27.4560546875</v>
+          <t>['c10::BFloat16', 'c10::BFloat16']</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>[[572416, 35776, 64, 1], [35776, 35776, 64, 1]]</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>['', '']</t>
+        </is>
       </c>
       <c r="AE7" t="n">
-        <v>0.2265912406627222</v>
+        <v>23.78922526041667</v>
       </c>
       <c r="AF7" t="n">
-        <v>26.9130859375</v>
+        <v>23.77587890625</v>
       </c>
       <c r="AG7" t="n">
-        <v>27.8720703125</v>
+        <v>0.1826717306685092</v>
       </c>
       <c r="AH7" t="n">
-        <v>658.080322265625</v>
+        <v>23.39208984375</v>
       </c>
       <c r="AI7" t="n">
-        <v>24</v>
+        <v>24.35205078125</v>
       </c>
       <c r="AJ7" t="n">
-        <v>179</v>
+        <v>1141.8828125</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aten::neg</t>
+          <t>aten::add</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(16, 16, 559, 32)</t>
+          <t>(16, 559, 1024)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', None)</t>
+          <t>(16, 559, 1024)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(572416, 64, 1024, 1)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>0.004579328</v>
-      </c>
-      <c r="G8" t="n">
-        <v>17.46875</v>
-      </c>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>(572416, 1024, 1)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>(572416, 1024, 1)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.25</v>
+        <v>0.009158655999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1.498114585099769</v>
+        <v>52.40625</v>
       </c>
       <c r="J8" t="n">
-        <v>1.502417196363491</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04096435731401789</v>
+        <v>3.088961333915809</v>
       </c>
       <c r="L8" t="n">
-        <v>1.379312619762846</v>
+        <v>3.077512782083186</v>
       </c>
       <c r="M8" t="n">
-        <v>1.576908088694592</v>
+        <v>0.08968722206012</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3745286462749423</v>
+        <v>2.890981284354651</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3756042990908726</v>
+        <v>3.221870998926439</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01024108932850447</v>
+        <v>0.5148268889859681</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3448281549407115</v>
+        <v>0.5129187970138642</v>
       </c>
       <c r="R8" t="n">
-        <v>0.394227022173648</v>
-      </c>
-      <c r="S8" t="inlineStr">
+        <v>0.01494787034335336</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4818302140591083</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.5369784998210732</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>thread 25286 (python3)</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(587.328), 'mean_duration_us': np.float64(12.235999999999999), 'median_duration_us': np.float64(12.192), 'std_dev_duration_us': np.float64(0.3355813363900522), 'min_duration_us': np.float64(11.616), 'max_duration_us': np.float64(13.28)}]</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(12.24)}]</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[[16, 16, 559, 32]]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'gpu_op_uid': 12139, 'count': 48, 'total_duration_us': np.float64(854.619), 'mean_duration_us': np.float64(17.8045625), 'median_duration_us': np.float64(17.856), 'std_dev_duration_us': np.float64(0.5150970744371872), 'min_duration_us': np.float64(17.056), 'max_duration_us': np.float64(19.008)}]</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>['c10::BFloat16']</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(17.8)}]</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>[[572416, 64, 1024, 1]]</t>
+          <t>[[16, 559, 1024], [16, 559, 1024], []]</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>['']</t>
-        </is>
-      </c>
-      <c r="AC8" t="n">
-        <v>12.23598225911458</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>12.19189453125</v>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>[[572416, 1024, 1], [572416, 1024, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>['', '', '1']</t>
+        </is>
       </c>
       <c r="AE8" t="n">
-        <v>0.339127372422647</v>
+        <v>17.80457051595052</v>
       </c>
       <c r="AF8" t="n">
-        <v>11.615966796875</v>
+        <v>17.85595703125</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.280029296875</v>
+        <v>0.5205274181052388</v>
       </c>
       <c r="AH8" t="n">
-        <v>587.3271484375</v>
+        <v>17.055908203125</v>
       </c>
       <c r="AI8" t="n">
+        <v>19.008056640625</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>854.619384765625</v>
+      </c>
+      <c r="AK8" t="n">
         <v>48</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>128</v>
+      <c r="AL8" t="n">
+        <v>191</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>aten::rsqrt</t>
+          <t>aten::add</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -17605,133 +17723,143 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>('float', None)</t>
+          <t>()</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>('float', 'double', None)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>(559, 1, 1)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>()</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
         <v>8.943999999999999e-06</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.0682373046875</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.125</v>
-      </c>
       <c r="I9" t="n">
-        <v>0.04448198949629482</v>
+        <v>0.06824493408203125</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04471727067439732</v>
+        <v>0.1249860257126887</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002337396261609372</v>
+        <v>0.04296483270099744</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03288196925838663</v>
+        <v>0.04384588780852655</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04658670990303609</v>
+        <v>0.002019140884211925</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005560248687036851</v>
+        <v>0.03666163352095059</v>
       </c>
       <c r="O9" t="n">
-        <v>0.005589658834299664</v>
+        <v>0.04563440137007629</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0002921745327011712</v>
+        <v>0.005370003684708232</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.004110246157298328</v>
+        <v>0.005480123261032161</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00582333873787951</v>
-      </c>
-      <c r="S9" t="inlineStr">
+        <v>0.0002523643944716527</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.004582191869918698</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.005703662463023508</v>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>thread 25286 (python3)</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>vector_fp32</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(79.073), 'mean_duration_us': np.float64(1.613734693877551), 'median_duration_us': np.float64(1.6), 'std_dev_duration_us': np.float64(0.10155782016738636), 'min_duration_us': np.float64(1.536), 'max_duration_us': np.float64(2.176)}]</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::rs...', 'stream': 7, 'mean_duration_us': np.float64(1.61)}]</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>[[16, 559, 1]]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 11991, 'count': 49, 'total_duration_us': np.float64(81.797), 'mean_duration_us': np.float64(1.669326530612245), 'median_duration_us': np.float64(1.632), 'std_dev_duration_us': np.float64(0.08264514449362109), 'min_duration_us': np.float64(1.568), 'max_duration_us': np.float64(1.952)}]</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>['float']</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.67)}]</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>[[559, 1, 1]]</t>
+          <t>[[16, 559, 1], [], []]</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>['']</t>
-        </is>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.613804408482143</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.60009765625</v>
+          <t>['float', 'double', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>[[559, 1, 1], [], []]</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>['', '', '1']</t>
+        </is>
       </c>
       <c r="AE9" t="n">
-        <v>0.1026021369823694</v>
+        <v>1.669383769132653</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.535888671875</v>
+        <v>1.632080078125</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.176025390625</v>
+        <v>0.0834552892669608</v>
       </c>
       <c r="AH9" t="n">
-        <v>79.076416015625</v>
+        <v>1.568115234375</v>
       </c>
       <c r="AI9" t="n">
+        <v>1.951904296875</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>81.7998046875</v>
+      </c>
+      <c r="AK9" t="n">
         <v>49</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>76</v>
+      <c r="AL9" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::mul</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -17741,265 +17869,137 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'float')</t>
+          <t>()</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>('float', 'double', None)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>(35776, 64, 1)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>(35776, 64, 1)</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>()</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
         <v>3.5776e-05</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.2047119140625</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.1666666666666667</v>
-      </c>
       <c r="I10" t="n">
-        <v>0.1443313768734171</v>
+        <v>0.2729568481445312</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1443313768734171</v>
+        <v>0.1249965061352265</v>
       </c>
       <c r="K10" t="n">
-        <v>0.002261434365022539</v>
+        <v>0.1825223004826405</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1427323012987013</v>
+        <v>0.1825223004826405</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1459304524481328</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.02405522947890284</v>
+        <v>0.1825223004826405</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02405522947890284</v>
+        <v>0.1825223004826405</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0003769057275037565</v>
+        <v>0.02281464985209403</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.02378871688311688</v>
+        <v>0.02281464985209403</v>
       </c>
       <c r="R10" t="n">
-        <v>0.02432174207468879</v>
-      </c>
-      <c r="S10" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.02281464985209403</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.02281464985209403</v>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>thread 25286 (python3)</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 2, 'total_duration_us': np.float64(2.975), 'mean_duration_us': np.float64(1.4875), 'median_duration_us': np.float64(1.4875), 'std_dev_duration_us': np.float64(0.01649999999999996), 'min_duration_us': np.float64(1.471), 'max_duration_us': np.float64(1.504)}]</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 7, 'mean_duration_us': np.float64(1.49)}]</t>
+          <t>vector_fp32</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>[[1, 559, 64], [1, 559, 64], []]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 11963, 'count': 2, 'total_duration_us': np.float64(3.136), 'mean_duration_us': np.float64(1.568), 'median_duration_us': np.float64(1.568), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.568), 'max_duration_us': np.float64(1.568)}]</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'float', 'Scalar']</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(1.57)}]</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>[[35776, 64, 1], [35776, 64, 1], []]</t>
+          <t>[[1, 559, 64], []]</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.4874267578125</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.4874267578125</v>
+          <t>['float', 'double']</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>[[35776, 64, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>['', '']</t>
+        </is>
       </c>
       <c r="AE10" t="n">
-        <v>0.02330552135258396</v>
+        <v>1.568115234375</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.470947265625</v>
+        <v>1.568115234375</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.50390625</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.974853515625</v>
+        <v>1.568115234375</v>
       </c>
       <c r="AI10" t="n">
+        <v>1.568115234375</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>3.13623046875</v>
+      </c>
+      <c r="AK10" t="n">
         <v>2</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>(1, 1, 559)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>('float', 'long int')</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>(559, 559, 1)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>(559, 559, 1)</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>5.59e-07</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.006397247314453125</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.00258792201186776</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.00258792201186776</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>0.00258792201186776</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.00258792201186776</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.0002156601676556466</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.0002156601676556466</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
-        <v>0.0002156601676556466</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.0002156601676556466</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>thread 25286 (python3)</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>vector_fp32</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.592), 'mean_duration_us': np.float64(2.592), 'median_duration_us': np.float64(2.592), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.592), 'max_duration_us': np.float64(2.592)}]</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(2.59)}]</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>[[1, 1, 559], [1, 1, 559], []]</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>['float', 'long int', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>[[559, 559, 1], [559, 559, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.592041015625</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.592041015625</v>
-      </c>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="n">
-        <v>2.592041015625</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.592041015625</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.592041015625</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>38</v>
+      <c r="AL10" t="n">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
